--- a/temp.xlsx
+++ b/temp.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="88">
   <si>
     <t>style</t>
   </si>
@@ -118,18 +118,18 @@
     <t>历史蔡</t>
   </si>
   <si>
-    <t>美术鉴赏张</t>
+    <t>音乐鉴赏孙</t>
   </si>
   <si>
     <t>英语蔺</t>
   </si>
   <si>
+    <t>信息技术杨</t>
+  </si>
+  <si>
     <t>物理纪</t>
   </si>
   <si>
-    <t>信息技术杨</t>
-  </si>
-  <si>
     <t>班会</t>
   </si>
   <si>
@@ -142,133 +142,118 @@
     <t>政治刘</t>
   </si>
   <si>
+    <t>地理单</t>
+  </si>
+  <si>
+    <t>化学刘</t>
+  </si>
+  <si>
+    <t>活动</t>
+  </si>
+  <si>
+    <t>生物郝</t>
+  </si>
+  <si>
     <t>体育苏</t>
   </si>
   <si>
-    <t>化学刘</t>
-  </si>
-  <si>
-    <t>活动</t>
-  </si>
-  <si>
-    <t>生物郝</t>
-  </si>
-  <si>
-    <t>地理单</t>
+    <t>阅读董</t>
+  </si>
+  <si>
+    <t>校本</t>
+  </si>
+  <si>
+    <t>语文车</t>
+  </si>
+  <si>
+    <t>体育张</t>
+  </si>
+  <si>
+    <t>阅读车</t>
+  </si>
+  <si>
+    <t>数学祝</t>
+  </si>
+  <si>
+    <t>政治婷</t>
+  </si>
+  <si>
+    <t>英语和</t>
+  </si>
+  <si>
+    <t>物理郭</t>
+  </si>
+  <si>
+    <t>英语侯</t>
+  </si>
+  <si>
+    <t>数学方</t>
+  </si>
+  <si>
+    <t>历史袁</t>
+  </si>
+  <si>
+    <t>日语</t>
+  </si>
+  <si>
+    <t>语文赵</t>
+  </si>
+  <si>
+    <t>数学涵</t>
+  </si>
+  <si>
+    <t>体育李</t>
+  </si>
+  <si>
+    <t>英语黎</t>
   </si>
   <si>
     <t>心理</t>
   </si>
   <si>
-    <t>校本</t>
-  </si>
-  <si>
-    <t>社团</t>
-  </si>
-  <si>
-    <t>语文车</t>
-  </si>
-  <si>
-    <t>体育张</t>
-  </si>
-  <si>
-    <t>数学祝</t>
-  </si>
-  <si>
-    <t>语文王</t>
-  </si>
-  <si>
-    <t>政治婷</t>
-  </si>
-  <si>
-    <t>英语和</t>
-  </si>
-  <si>
-    <t>物理郭</t>
-  </si>
-  <si>
-    <t>英语黎</t>
-  </si>
-  <si>
-    <t>数学方</t>
-  </si>
-  <si>
-    <t>体育李</t>
-  </si>
-  <si>
-    <t>英语侯</t>
-  </si>
-  <si>
-    <t>历史袁</t>
-  </si>
-  <si>
-    <t>专业课</t>
-  </si>
-  <si>
-    <t>日语</t>
-  </si>
-  <si>
     <t>生物邵</t>
   </si>
   <si>
-    <t>数学涵</t>
-  </si>
-  <si>
-    <t>语文赵</t>
-  </si>
-  <si>
     <t>化学任</t>
   </si>
   <si>
-    <t>阅读赵</t>
+    <t>英语孙</t>
+  </si>
+  <si>
+    <t>地理陈</t>
+  </si>
+  <si>
+    <t>政治孙</t>
   </si>
   <si>
     <t>技术田</t>
   </si>
   <si>
-    <t>音乐鉴赏孙</t>
-  </si>
-  <si>
-    <t>政治孙</t>
-  </si>
-  <si>
-    <t>英语孙</t>
-  </si>
-  <si>
-    <t>地理陈</t>
-  </si>
-  <si>
     <t>数学戴</t>
   </si>
   <si>
-    <t>语文刘</t>
-  </si>
-  <si>
-    <t>阅读刘</t>
+    <t>体育曲</t>
+  </si>
+  <si>
+    <t>日语宋</t>
+  </si>
+  <si>
+    <t>英语赵</t>
+  </si>
+  <si>
+    <t>历史苏</t>
+  </si>
+  <si>
+    <t>语文孙</t>
+  </si>
+  <si>
+    <t>数学朱</t>
+  </si>
+  <si>
+    <t>地理隋</t>
   </si>
   <si>
     <t>体育赵</t>
-  </si>
-  <si>
-    <t>体育曲</t>
-  </si>
-  <si>
-    <t>日语宋</t>
-  </si>
-  <si>
-    <t>英语赵</t>
-  </si>
-  <si>
-    <t>数学朱</t>
-  </si>
-  <si>
-    <t>地理隋</t>
-  </si>
-  <si>
-    <t>历史苏</t>
-  </si>
-  <si>
-    <t>语文孙</t>
   </si>
   <si>
     <t>英语段</t>
@@ -732,7 +717,7 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -806,7 +791,7 @@
         <v>24</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -824,52 +809,52 @@
         <v>52</v>
       </c>
       <c r="I3" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="K3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" t="s">
         <v>60</v>
       </c>
-      <c r="L3" t="s">
-        <v>63</v>
-      </c>
-      <c r="M3" t="s">
-        <v>64</v>
-      </c>
       <c r="N3" t="s">
+        <v>67</v>
+      </c>
+      <c r="O3" t="s">
         <v>71</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" t="s">
+        <v>74</v>
+      </c>
+      <c r="S3" t="s">
+        <v>80</v>
+      </c>
+      <c r="T3" t="s">
+        <v>83</v>
+      </c>
+      <c r="U3" t="s">
         <v>73</v>
       </c>
-      <c r="P3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" t="s">
-        <v>80</v>
-      </c>
-      <c r="S3" t="s">
-        <v>85</v>
-      </c>
-      <c r="T3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U3" t="s">
-        <v>79</v>
-      </c>
       <c r="V3" t="s">
         <v>30</v>
       </c>
       <c r="W3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="X3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -880,7 +865,7 @@
         <v>24</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -892,46 +877,46 @@
         <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N4" t="s">
         <v>58</v>
       </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" t="s">
-        <v>65</v>
-      </c>
-      <c r="N4" t="s">
-        <v>61</v>
-      </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>30</v>
+      </c>
+      <c r="R4" t="s">
         <v>75</v>
       </c>
-      <c r="Q4" t="s">
-        <v>30</v>
-      </c>
-      <c r="R4" t="s">
-        <v>54</v>
-      </c>
       <c r="S4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="T4" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="U4" t="s">
         <v>30</v>
@@ -940,10 +925,10 @@
         <v>30</v>
       </c>
       <c r="W4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="X4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -954,7 +939,7 @@
         <v>24</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -966,47 +951,47 @@
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
         <v>43</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" t="s">
         <v>58</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" t="s">
         <v>61</v>
       </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N5" t="s">
-        <v>65</v>
-      </c>
       <c r="O5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="s">
         <v>30</v>
       </c>
       <c r="R5" t="s">
+        <v>76</v>
+      </c>
+      <c r="S5" t="s">
+        <v>79</v>
+      </c>
+      <c r="T5" t="s">
         <v>81</v>
       </c>
-      <c r="S5" t="s">
-        <v>86</v>
-      </c>
-      <c r="T5" t="s">
-        <v>84</v>
-      </c>
       <c r="U5" t="s">
         <v>30</v>
       </c>
@@ -1014,10 +999,10 @@
         <v>30</v>
       </c>
       <c r="W5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="X5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -1028,7 +1013,7 @@
         <v>24</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1043,13 +1028,13 @@
         <v>33</v>
       </c>
       <c r="H6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K6" t="s">
         <v>31</v>
@@ -1058,40 +1043,40 @@
         <v>30</v>
       </c>
       <c r="M6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>72</v>
+      </c>
+      <c r="R6" t="s">
         <v>77</v>
       </c>
-      <c r="Q6" t="s">
-        <v>78</v>
-      </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
+        <v>81</v>
+      </c>
+      <c r="T6" t="s">
+        <v>76</v>
+      </c>
+      <c r="U6" t="s">
+        <v>30</v>
+      </c>
+      <c r="V6" t="s">
+        <v>30</v>
+      </c>
+      <c r="W6" t="s">
         <v>82</v>
       </c>
-      <c r="S6" t="s">
-        <v>54</v>
-      </c>
-      <c r="T6" t="s">
-        <v>64</v>
-      </c>
-      <c r="U6" t="s">
-        <v>30</v>
-      </c>
-      <c r="V6" t="s">
-        <v>30</v>
-      </c>
-      <c r="W6" t="s">
-        <v>91</v>
-      </c>
       <c r="X6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -1102,7 +1087,7 @@
         <v>24</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1117,43 +1102,43 @@
         <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I7" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="K7" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="L7" t="s">
         <v>30</v>
       </c>
       <c r="M7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N7" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="O7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="P7" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="Q7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="R7" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="S7" t="s">
         <v>82</v>
       </c>
       <c r="T7" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="U7" t="s">
         <v>30</v>
@@ -1162,10 +1147,10 @@
         <v>30</v>
       </c>
       <c r="W7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="X7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1176,7 +1161,7 @@
         <v>24</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1188,58 +1173,58 @@
         <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I8" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="L8" t="s">
         <v>30</v>
       </c>
       <c r="M8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O8" t="s">
+        <v>58</v>
+      </c>
+      <c r="P8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R8" t="s">
+        <v>53</v>
+      </c>
+      <c r="S8" t="s">
         <v>75</v>
       </c>
-      <c r="P8" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>30</v>
-      </c>
-      <c r="R8" t="s">
-        <v>77</v>
-      </c>
-      <c r="S8" t="s">
-        <v>87</v>
-      </c>
       <c r="T8" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="U8" t="s">
         <v>30</v>
       </c>
       <c r="V8" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="W8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="X8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1250,7 +1235,7 @@
         <v>24</v>
       </c>
       <c r="C9">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1265,55 +1250,55 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J9" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="K9" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L9" t="s">
         <v>30</v>
       </c>
       <c r="M9" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" t="s">
         <v>67</v>
       </c>
-      <c r="N9" t="s">
-        <v>73</v>
-      </c>
       <c r="O9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P9" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="Q9" t="s">
         <v>30</v>
       </c>
       <c r="R9" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="S9" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="T9" t="s">
+        <v>39</v>
+      </c>
+      <c r="U9" t="s">
+        <v>30</v>
+      </c>
+      <c r="V9" t="s">
+        <v>30</v>
+      </c>
+      <c r="W9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X9" t="s">
         <v>86</v>
-      </c>
-      <c r="U9" t="s">
-        <v>30</v>
-      </c>
-      <c r="V9" t="s">
-        <v>30</v>
-      </c>
-      <c r="W9" t="s">
-        <v>87</v>
-      </c>
-      <c r="X9" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -1324,7 +1309,7 @@
         <v>24</v>
       </c>
       <c r="C10">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1342,13 +1327,13 @@
         <v>38</v>
       </c>
       <c r="I10" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J10" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K10" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L10" t="s">
         <v>30</v>
@@ -1363,7 +1348,7 @@
         <v>38</v>
       </c>
       <c r="P10" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Q10" t="s">
         <v>38</v>
@@ -1398,7 +1383,7 @@
         <v>25</v>
       </c>
       <c r="C11">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1413,43 +1398,43 @@
         <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="J11" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K11" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="L11" t="s">
         <v>30</v>
       </c>
       <c r="M11" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N11" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="O11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="P11" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="Q11" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="R11" t="s">
+        <v>77</v>
+      </c>
+      <c r="S11" t="s">
         <v>81</v>
       </c>
-      <c r="S11" t="s">
-        <v>86</v>
-      </c>
       <c r="T11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="U11" t="s">
         <v>30</v>
@@ -1458,10 +1443,10 @@
         <v>30</v>
       </c>
       <c r="W11" t="s">
+        <v>82</v>
+      </c>
+      <c r="X11" t="s">
         <v>87</v>
-      </c>
-      <c r="X11" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1472,7 +1457,7 @@
         <v>25</v>
       </c>
       <c r="C12">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1487,55 +1472,55 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J12" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="K12" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" t="s">
+        <v>30</v>
+      </c>
+      <c r="M12" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12" t="s">
+        <v>67</v>
+      </c>
+      <c r="O12" t="s">
         <v>60</v>
       </c>
-      <c r="L12" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" t="s">
-        <v>65</v>
-      </c>
-      <c r="N12" t="s">
-        <v>72</v>
-      </c>
-      <c r="O12" t="s">
-        <v>75</v>
-      </c>
       <c r="P12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R12" t="s">
+        <v>76</v>
+      </c>
+      <c r="S12" t="s">
+        <v>82</v>
+      </c>
+      <c r="T12" t="s">
+        <v>81</v>
+      </c>
+      <c r="U12" t="s">
+        <v>30</v>
+      </c>
+      <c r="V12" t="s">
+        <v>73</v>
+      </c>
+      <c r="W12" t="s">
+        <v>80</v>
+      </c>
+      <c r="X12" t="s">
         <v>74</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>30</v>
-      </c>
-      <c r="R12" t="s">
-        <v>84</v>
-      </c>
-      <c r="S12" t="s">
-        <v>87</v>
-      </c>
-      <c r="T12" t="s">
-        <v>86</v>
-      </c>
-      <c r="U12" t="s">
-        <v>30</v>
-      </c>
-      <c r="V12" t="s">
-        <v>79</v>
-      </c>
-      <c r="W12" t="s">
-        <v>85</v>
-      </c>
-      <c r="X12" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -1546,7 +1531,7 @@
         <v>25</v>
       </c>
       <c r="C13">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1558,58 +1543,58 @@
         <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H13" t="s">
         <v>52</v>
       </c>
       <c r="I13" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J13" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="K13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L13" t="s">
         <v>30</v>
       </c>
       <c r="M13" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="O13" t="s">
+        <v>71</v>
+      </c>
+      <c r="P13" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>30</v>
+      </c>
+      <c r="R13" t="s">
         <v>74</v>
       </c>
-      <c r="P13" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>30</v>
-      </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>80</v>
       </c>
-      <c r="S13" t="s">
-        <v>85</v>
-      </c>
       <c r="T13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="U13" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="V13" t="s">
         <v>30</v>
       </c>
       <c r="W13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="X13" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -1620,7 +1605,7 @@
         <v>25</v>
       </c>
       <c r="C14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1638,13 +1623,13 @@
         <v>39</v>
       </c>
       <c r="I14" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J14" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L14" t="s">
         <v>30</v>
@@ -1659,7 +1644,7 @@
         <v>39</v>
       </c>
       <c r="P14" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="Q14" t="s">
         <v>30</v>
@@ -1694,7 +1679,7 @@
         <v>23</v>
       </c>
       <c r="C15">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -1712,13 +1697,13 @@
         <v>40</v>
       </c>
       <c r="I15" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J15" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K15" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L15" t="s">
         <v>30</v>
@@ -1733,7 +1718,7 @@
         <v>40</v>
       </c>
       <c r="P15" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q15" t="s">
         <v>30</v>
@@ -1768,7 +1753,7 @@
         <v>24</v>
       </c>
       <c r="C16">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1777,49 +1762,49 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G16" t="s">
         <v>32</v>
       </c>
       <c r="H16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I16" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="K16" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="L16" t="s">
         <v>30</v>
       </c>
       <c r="M16" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N16" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P16" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="Q16" t="s">
         <v>30</v>
       </c>
       <c r="R16" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="S16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T16" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="U16" t="s">
         <v>30</v>
@@ -1828,10 +1813,10 @@
         <v>30</v>
       </c>
       <c r="W16" t="s">
+        <v>82</v>
+      </c>
+      <c r="X16" t="s">
         <v>87</v>
-      </c>
-      <c r="X16" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -1842,7 +1827,7 @@
         <v>24</v>
       </c>
       <c r="C17">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1854,46 +1839,46 @@
         <v>35</v>
       </c>
       <c r="G17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I17" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="J17" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="K17" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="L17" t="s">
         <v>30</v>
       </c>
       <c r="M17" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="O17" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="P17" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="Q17" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="R17" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="S17" t="s">
         <v>82</v>
       </c>
       <c r="T17" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="U17" t="s">
         <v>30</v>
@@ -1902,10 +1887,10 @@
         <v>30</v>
       </c>
       <c r="W17" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="X17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -1916,7 +1901,7 @@
         <v>24</v>
       </c>
       <c r="C18">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1934,52 +1919,52 @@
         <v>52</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J18" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="K18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L18" t="s">
         <v>30</v>
       </c>
       <c r="M18" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N18" t="s">
+        <v>68</v>
+      </c>
+      <c r="O18" t="s">
+        <v>58</v>
+      </c>
+      <c r="P18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>30</v>
+      </c>
+      <c r="R18" t="s">
+        <v>74</v>
+      </c>
+      <c r="S18" t="s">
+        <v>80</v>
+      </c>
+      <c r="T18" t="s">
+        <v>83</v>
+      </c>
+      <c r="U18" t="s">
         <v>73</v>
       </c>
-      <c r="O18" t="s">
-        <v>61</v>
-      </c>
-      <c r="P18" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>30</v>
-      </c>
-      <c r="R18" t="s">
-        <v>80</v>
-      </c>
-      <c r="S18" t="s">
-        <v>85</v>
-      </c>
-      <c r="T18" t="s">
-        <v>88</v>
-      </c>
-      <c r="U18" t="s">
-        <v>79</v>
-      </c>
       <c r="V18" t="s">
         <v>30</v>
       </c>
       <c r="W18" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="X18" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -1990,7 +1975,7 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2002,58 +1987,58 @@
         <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I19" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J19" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" t="s">
+        <v>30</v>
+      </c>
+      <c r="L19" t="s">
+        <v>30</v>
+      </c>
+      <c r="M19" t="s">
+        <v>61</v>
+      </c>
+      <c r="N19" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" t="s">
         <v>34</v>
       </c>
-      <c r="K19" t="s">
-        <v>46</v>
-      </c>
-      <c r="L19" t="s">
-        <v>30</v>
-      </c>
-      <c r="M19" t="s">
-        <v>65</v>
-      </c>
-      <c r="N19" t="s">
-        <v>66</v>
-      </c>
-      <c r="O19" t="s">
-        <v>70</v>
-      </c>
       <c r="P19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>30</v>
+      </c>
+      <c r="R19" t="s">
+        <v>77</v>
+      </c>
+      <c r="S19" t="s">
+        <v>82</v>
+      </c>
+      <c r="T19" t="s">
+        <v>76</v>
+      </c>
+      <c r="U19" t="s">
+        <v>30</v>
+      </c>
+      <c r="V19" t="s">
         <v>73</v>
       </c>
-      <c r="Q19" t="s">
-        <v>30</v>
-      </c>
-      <c r="R19" t="s">
-        <v>81</v>
-      </c>
-      <c r="S19" t="s">
-        <v>86</v>
-      </c>
-      <c r="T19" t="s">
-        <v>84</v>
-      </c>
-      <c r="U19" t="s">
-        <v>30</v>
-      </c>
-      <c r="V19" t="s">
-        <v>79</v>
-      </c>
       <c r="W19" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="X19" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2064,7 +2049,7 @@
         <v>24</v>
       </c>
       <c r="C20">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -2079,55 +2064,55 @@
         <v>45</v>
       </c>
       <c r="H20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I20" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J20" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L20" t="s">
         <v>30</v>
       </c>
       <c r="M20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O20" t="s">
+        <v>68</v>
+      </c>
+      <c r="P20" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>30</v>
+      </c>
+      <c r="R20" t="s">
+        <v>74</v>
+      </c>
+      <c r="S20" t="s">
+        <v>80</v>
+      </c>
+      <c r="T20" t="s">
+        <v>83</v>
+      </c>
+      <c r="U20" t="s">
         <v>73</v>
       </c>
-      <c r="P20" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>30</v>
-      </c>
-      <c r="R20" t="s">
+      <c r="V20" t="s">
+        <v>30</v>
+      </c>
+      <c r="W20" t="s">
         <v>84</v>
       </c>
-      <c r="S20" t="s">
-        <v>86</v>
-      </c>
-      <c r="T20" t="s">
-        <v>39</v>
-      </c>
-      <c r="U20" t="s">
-        <v>30</v>
-      </c>
-      <c r="V20" t="s">
-        <v>30</v>
-      </c>
-      <c r="W20" t="s">
-        <v>89</v>
-      </c>
       <c r="X20" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2138,7 +2123,7 @@
         <v>24</v>
       </c>
       <c r="C21">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -2150,46 +2135,46 @@
         <v>43</v>
       </c>
       <c r="G21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H21" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="I21" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="J21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M21" t="s">
+        <v>55</v>
+      </c>
+      <c r="N21" t="s">
         <v>58</v>
       </c>
-      <c r="K21" t="s">
-        <v>41</v>
-      </c>
-      <c r="L21" t="s">
-        <v>30</v>
-      </c>
-      <c r="M21" t="s">
-        <v>56</v>
-      </c>
-      <c r="N21" t="s">
-        <v>61</v>
-      </c>
       <c r="O21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P21" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="Q21" t="s">
         <v>30</v>
       </c>
       <c r="R21" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="S21" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="T21" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="U21" t="s">
         <v>30</v>
@@ -2198,10 +2183,10 @@
         <v>30</v>
       </c>
       <c r="W21" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="X21" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:24">
@@ -2212,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="C22">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -2221,50 +2206,50 @@
         <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
         <v>34</v>
       </c>
       <c r="H22" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I22" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="J22" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="K22" t="s">
+        <v>30</v>
+      </c>
+      <c r="L22" t="s">
+        <v>59</v>
+      </c>
+      <c r="M22" t="s">
+        <v>66</v>
+      </c>
+      <c r="N22" t="s">
+        <v>61</v>
+      </c>
+      <c r="O22" t="s">
         <v>60</v>
       </c>
-      <c r="L22" t="s">
-        <v>63</v>
-      </c>
-      <c r="M22" t="s">
-        <v>68</v>
-      </c>
-      <c r="N22" t="s">
+      <c r="P22" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>30</v>
+      </c>
+      <c r="R22" t="s">
+        <v>78</v>
+      </c>
+      <c r="S22" t="s">
+        <v>81</v>
+      </c>
+      <c r="T22" t="s">
         <v>65</v>
       </c>
-      <c r="O22" t="s">
-        <v>75</v>
-      </c>
-      <c r="P22" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>30</v>
-      </c>
-      <c r="R22" t="s">
-        <v>82</v>
-      </c>
-      <c r="S22" t="s">
-        <v>54</v>
-      </c>
-      <c r="T22" t="s">
-        <v>64</v>
-      </c>
       <c r="U22" t="s">
         <v>30</v>
       </c>
@@ -2272,10 +2257,10 @@
         <v>30</v>
       </c>
       <c r="W22" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="X22" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -2286,7 +2271,7 @@
         <v>24</v>
       </c>
       <c r="C23">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -2304,31 +2289,31 @@
         <v>44</v>
       </c>
       <c r="I23" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="J23" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="K23" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L23" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="M23" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N23" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P23" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="Q23" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="R23" t="s">
         <v>39</v>
@@ -2360,7 +2345,7 @@
         <v>25</v>
       </c>
       <c r="C24">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -2375,43 +2360,43 @@
         <v>45</v>
       </c>
       <c r="H24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I24" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="J24" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K24" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="L24" t="s">
         <v>30</v>
       </c>
       <c r="M24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O24" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="P24" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="Q24" t="s">
         <v>30</v>
       </c>
       <c r="R24" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="S24" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="T24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U24" t="s">
         <v>30</v>
@@ -2420,10 +2405,10 @@
         <v>30</v>
       </c>
       <c r="W24" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="X24" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:24">
@@ -2434,7 +2419,7 @@
         <v>25</v>
       </c>
       <c r="C25">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -2446,46 +2431,46 @@
         <v>45</v>
       </c>
       <c r="G25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H25" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I25" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="J25" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="K25" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L25" t="s">
         <v>30</v>
       </c>
       <c r="M25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N25" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P25" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="Q25" t="s">
         <v>30</v>
       </c>
       <c r="R25" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="S25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U25" t="s">
         <v>30</v>
@@ -2494,10 +2479,10 @@
         <v>30</v>
       </c>
       <c r="W25" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="X25" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:24">
@@ -2508,7 +2493,7 @@
         <v>25</v>
       </c>
       <c r="C26">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -2523,43 +2508,43 @@
         <v>39</v>
       </c>
       <c r="H26" t="s">
+        <v>49</v>
+      </c>
+      <c r="I26" t="s">
+        <v>30</v>
+      </c>
+      <c r="J26" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" t="s">
+        <v>30</v>
+      </c>
+      <c r="L26" t="s">
+        <v>30</v>
+      </c>
+      <c r="M26" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" t="s">
+        <v>68</v>
+      </c>
+      <c r="O26" t="s">
+        <v>58</v>
+      </c>
+      <c r="P26" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>30</v>
+      </c>
+      <c r="R26" t="s">
         <v>53</v>
       </c>
-      <c r="I26" t="s">
+      <c r="S26" t="s">
         <v>39</v>
       </c>
-      <c r="J26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K26" t="s">
-        <v>31</v>
-      </c>
-      <c r="L26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M26" t="s">
-        <v>56</v>
-      </c>
-      <c r="N26" t="s">
-        <v>73</v>
-      </c>
-      <c r="O26" t="s">
-        <v>61</v>
-      </c>
-      <c r="P26" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>30</v>
-      </c>
-      <c r="R26" t="s">
-        <v>54</v>
-      </c>
-      <c r="S26" t="s">
-        <v>83</v>
-      </c>
       <c r="T26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U26" t="s">
         <v>30</v>
@@ -2568,10 +2553,10 @@
         <v>30</v>
       </c>
       <c r="W26" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="X26" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:24">
@@ -2582,7 +2567,7 @@
         <v>25</v>
       </c>
       <c r="C27">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -2600,13 +2585,13 @@
         <v>39</v>
       </c>
       <c r="I27" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J27" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="K27" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L27" t="s">
         <v>30</v>
@@ -2621,7 +2606,7 @@
         <v>39</v>
       </c>
       <c r="P27" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="Q27" t="s">
         <v>30</v>
@@ -2656,7 +2641,7 @@
         <v>23</v>
       </c>
       <c r="C28">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -2674,13 +2659,13 @@
         <v>40</v>
       </c>
       <c r="I28" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J28" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K28" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L28" t="s">
         <v>30</v>
@@ -2695,7 +2680,7 @@
         <v>40</v>
       </c>
       <c r="P28" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q28" t="s">
         <v>30</v>
@@ -2730,7 +2715,7 @@
         <v>24</v>
       </c>
       <c r="C29">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -2745,55 +2730,55 @@
         <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="I29" t="s">
+        <v>30</v>
+      </c>
+      <c r="J29" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" t="s">
+        <v>30</v>
+      </c>
+      <c r="L29" t="s">
+        <v>59</v>
+      </c>
+      <c r="M29" t="s">
+        <v>61</v>
+      </c>
+      <c r="N29" t="s">
+        <v>68</v>
+      </c>
+      <c r="O29" t="s">
+        <v>58</v>
+      </c>
+      <c r="P29" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>30</v>
+      </c>
+      <c r="R29" t="s">
         <v>53</v>
       </c>
-      <c r="J29" t="s">
-        <v>56</v>
-      </c>
-      <c r="K29" t="s">
-        <v>58</v>
-      </c>
-      <c r="L29" t="s">
-        <v>30</v>
-      </c>
-      <c r="M29" t="s">
-        <v>67</v>
-      </c>
-      <c r="N29" t="s">
+      <c r="S29" t="s">
+        <v>75</v>
+      </c>
+      <c r="T29" t="s">
+        <v>37</v>
+      </c>
+      <c r="U29" t="s">
+        <v>30</v>
+      </c>
+      <c r="V29" t="s">
         <v>73</v>
       </c>
-      <c r="O29" t="s">
-        <v>61</v>
-      </c>
-      <c r="P29" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>30</v>
-      </c>
-      <c r="R29" t="s">
-        <v>84</v>
-      </c>
-      <c r="S29" t="s">
-        <v>87</v>
-      </c>
-      <c r="T29" t="s">
-        <v>86</v>
-      </c>
-      <c r="U29" t="s">
-        <v>30</v>
-      </c>
-      <c r="V29" t="s">
-        <v>79</v>
-      </c>
       <c r="W29" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="X29" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:24">
@@ -2804,7 +2789,7 @@
         <v>24</v>
       </c>
       <c r="C30">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -2816,58 +2801,58 @@
         <v>41</v>
       </c>
       <c r="G30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J30" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="K30" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L30" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="M30" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="N30" t="s">
         <v>69</v>
       </c>
       <c r="O30" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P30" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="Q30" t="s">
         <v>30</v>
       </c>
       <c r="R30" t="s">
+        <v>77</v>
+      </c>
+      <c r="S30" t="s">
         <v>81</v>
       </c>
-      <c r="S30" t="s">
+      <c r="T30" t="s">
+        <v>66</v>
+      </c>
+      <c r="U30" t="s">
+        <v>30</v>
+      </c>
+      <c r="V30" t="s">
+        <v>30</v>
+      </c>
+      <c r="W30" t="s">
         <v>86</v>
       </c>
-      <c r="T30" t="s">
-        <v>84</v>
-      </c>
-      <c r="U30" t="s">
-        <v>30</v>
-      </c>
-      <c r="V30" t="s">
-        <v>30</v>
-      </c>
-      <c r="W30" t="s">
-        <v>91</v>
-      </c>
       <c r="X30" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:24">
@@ -2878,7 +2863,7 @@
         <v>24</v>
       </c>
       <c r="C31">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -2887,61 +2872,61 @@
         <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G31" t="s">
         <v>32</v>
       </c>
       <c r="H31" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="I31" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J31" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="K31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L31" t="s">
         <v>30</v>
       </c>
       <c r="M31" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N31" t="s">
+        <v>61</v>
+      </c>
+      <c r="O31" t="s">
+        <v>67</v>
+      </c>
+      <c r="P31" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>73</v>
+      </c>
+      <c r="R31" t="s">
+        <v>77</v>
+      </c>
+      <c r="S31" t="s">
+        <v>53</v>
+      </c>
+      <c r="T31" t="s">
         <v>65</v>
       </c>
-      <c r="O31" t="s">
-        <v>72</v>
-      </c>
-      <c r="P31" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>79</v>
-      </c>
-      <c r="R31" t="s">
+      <c r="U31" t="s">
+        <v>30</v>
+      </c>
+      <c r="V31" t="s">
+        <v>30</v>
+      </c>
+      <c r="W31" t="s">
         <v>82</v>
       </c>
-      <c r="S31" t="s">
-        <v>54</v>
-      </c>
-      <c r="T31" t="s">
-        <v>64</v>
-      </c>
-      <c r="U31" t="s">
-        <v>30</v>
-      </c>
-      <c r="V31" t="s">
-        <v>30</v>
-      </c>
-      <c r="W31" t="s">
-        <v>81</v>
-      </c>
       <c r="X31" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:24">
@@ -2952,7 +2937,7 @@
         <v>24</v>
       </c>
       <c r="C32">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D32">
         <v>3</v>
@@ -2961,49 +2946,49 @@
         <v>4</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G32" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H32" t="s">
         <v>52</v>
       </c>
       <c r="I32" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="J32" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="K32" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="L32" t="s">
         <v>30</v>
       </c>
       <c r="M32" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N32" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O32" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="P32" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="Q32" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="R32" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="S32" t="s">
         <v>82</v>
       </c>
       <c r="T32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U32" t="s">
         <v>30</v>
@@ -3012,10 +2997,10 @@
         <v>30</v>
       </c>
       <c r="W32" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="X32" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:24">
@@ -3026,7 +3011,7 @@
         <v>24</v>
       </c>
       <c r="C33">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D33">
         <v>3</v>
@@ -3035,61 +3020,61 @@
         <v>5</v>
       </c>
       <c r="F33" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G33" t="s">
         <v>33</v>
       </c>
       <c r="H33" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I33" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J33" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K33" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L33" t="s">
         <v>30</v>
       </c>
       <c r="M33" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N33" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O33" t="s">
+        <v>71</v>
+      </c>
+      <c r="P33" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>30</v>
+      </c>
+      <c r="R33" t="s">
         <v>74</v>
       </c>
-      <c r="P33" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>30</v>
-      </c>
-      <c r="R33" t="s">
+      <c r="S33" t="s">
         <v>80</v>
       </c>
-      <c r="S33" t="s">
-        <v>85</v>
-      </c>
       <c r="T33" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="U33" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="V33" t="s">
         <v>30</v>
       </c>
       <c r="W33" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="X33" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:24">
@@ -3100,7 +3085,7 @@
         <v>24</v>
       </c>
       <c r="C34">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -3109,61 +3094,61 @@
         <v>6</v>
       </c>
       <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" t="s">
         <v>35</v>
       </c>
-      <c r="G34" t="s">
-        <v>46</v>
-      </c>
       <c r="H34" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I34" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J34" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K34" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="L34" t="s">
         <v>30</v>
       </c>
       <c r="M34" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N34" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O34" t="s">
+        <v>60</v>
+      </c>
+      <c r="P34" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>30</v>
+      </c>
+      <c r="R34" t="s">
         <v>74</v>
       </c>
-      <c r="P34" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>30</v>
-      </c>
-      <c r="R34" t="s">
+      <c r="S34" t="s">
         <v>80</v>
       </c>
-      <c r="S34" t="s">
+      <c r="T34" t="s">
+        <v>83</v>
+      </c>
+      <c r="U34" t="s">
+        <v>73</v>
+      </c>
+      <c r="V34" t="s">
+        <v>30</v>
+      </c>
+      <c r="W34" t="s">
+        <v>84</v>
+      </c>
+      <c r="X34" t="s">
         <v>85</v>
-      </c>
-      <c r="T34" t="s">
-        <v>88</v>
-      </c>
-      <c r="U34" t="s">
-        <v>79</v>
-      </c>
-      <c r="V34" t="s">
-        <v>30</v>
-      </c>
-      <c r="W34" t="s">
-        <v>89</v>
-      </c>
-      <c r="X34" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:24">
@@ -3174,7 +3159,7 @@
         <v>24</v>
       </c>
       <c r="C35">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -3183,49 +3168,49 @@
         <v>7</v>
       </c>
       <c r="F35" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G35" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I35" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="J35" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="K35" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L35" t="s">
         <v>30</v>
       </c>
       <c r="M35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N35" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="O35" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P35" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="Q35" t="s">
         <v>30</v>
       </c>
       <c r="R35" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="S35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T35" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="U35" t="s">
         <v>30</v>
@@ -3234,10 +3219,10 @@
         <v>30</v>
       </c>
       <c r="W35" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="X35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:24">
@@ -3248,7 +3233,7 @@
         <v>24</v>
       </c>
       <c r="C36">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D36">
         <v>3</v>
@@ -3266,13 +3251,13 @@
         <v>44</v>
       </c>
       <c r="I36" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="J36" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="K36" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L36" t="s">
         <v>30</v>
@@ -3287,7 +3272,7 @@
         <v>44</v>
       </c>
       <c r="P36" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="Q36" t="s">
         <v>30</v>
@@ -3322,7 +3307,7 @@
         <v>25</v>
       </c>
       <c r="C37">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -3337,16 +3322,16 @@
         <v>33</v>
       </c>
       <c r="H37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I37" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J37" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="K37" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="L37" t="s">
         <v>30</v>
@@ -3355,25 +3340,25 @@
         <v>39</v>
       </c>
       <c r="N37" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="O37" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P37" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="Q37" t="s">
         <v>30</v>
       </c>
       <c r="R37" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="S37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U37" t="s">
         <v>30</v>
@@ -3382,10 +3367,10 @@
         <v>30</v>
       </c>
       <c r="W37" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="X37" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:24">
@@ -3396,7 +3381,7 @@
         <v>25</v>
       </c>
       <c r="C38">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -3405,7 +3390,7 @@
         <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G38" t="s">
         <v>35</v>
@@ -3414,40 +3399,40 @@
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="J38" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K38" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="L38" t="s">
         <v>30</v>
       </c>
       <c r="M38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N38" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O38" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="P38" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="Q38" t="s">
         <v>30</v>
       </c>
       <c r="R38" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="S38" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="T38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U38" t="s">
         <v>30</v>
@@ -3456,10 +3441,10 @@
         <v>30</v>
       </c>
       <c r="W38" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="X38" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:24">
@@ -3470,7 +3455,7 @@
         <v>25</v>
       </c>
       <c r="C39">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -3488,40 +3473,40 @@
         <v>39</v>
       </c>
       <c r="I39" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J39" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="K39" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L39" t="s">
         <v>30</v>
       </c>
       <c r="M39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N39" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P39" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="Q39" t="s">
         <v>30</v>
       </c>
       <c r="R39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S39" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="T39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U39" t="s">
         <v>30</v>
@@ -3530,10 +3515,10 @@
         <v>30</v>
       </c>
       <c r="W39" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="X39" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:24">
@@ -3544,7 +3529,7 @@
         <v>25</v>
       </c>
       <c r="C40">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -3562,13 +3547,13 @@
         <v>39</v>
       </c>
       <c r="I40" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J40" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="K40" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L40" t="s">
         <v>30</v>
@@ -3583,7 +3568,7 @@
         <v>39</v>
       </c>
       <c r="P40" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="Q40" t="s">
         <v>30</v>
@@ -3618,7 +3603,7 @@
         <v>23</v>
       </c>
       <c r="C41">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -3636,13 +3621,13 @@
         <v>40</v>
       </c>
       <c r="I41" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J41" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K41" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L41" t="s">
         <v>30</v>
@@ -3657,7 +3642,7 @@
         <v>40</v>
       </c>
       <c r="P41" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q41" t="s">
         <v>30</v>
@@ -3692,7 +3677,7 @@
         <v>24</v>
       </c>
       <c r="C42">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -3701,13 +3686,13 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G42" t="s">
         <v>32</v>
       </c>
       <c r="H42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I42" t="s">
         <v>30</v>
@@ -3716,19 +3701,19 @@
         <v>30</v>
       </c>
       <c r="K42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L42" t="s">
         <v>30</v>
       </c>
       <c r="M42" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N42" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="O42" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P42" t="s">
         <v>30</v>
@@ -3737,13 +3722,13 @@
         <v>30</v>
       </c>
       <c r="R42" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="S42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U42" t="s">
         <v>30</v>
@@ -3752,10 +3737,10 @@
         <v>30</v>
       </c>
       <c r="W42" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="X42" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:24">
@@ -3766,7 +3751,7 @@
         <v>24</v>
       </c>
       <c r="C43">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -3775,13 +3760,13 @@
         <v>2</v>
       </c>
       <c r="F43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G43" t="s">
         <v>45</v>
       </c>
       <c r="H43" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I43" t="s">
         <v>30</v>
@@ -3790,19 +3775,19 @@
         <v>30</v>
       </c>
       <c r="K43" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="L43" t="s">
         <v>30</v>
       </c>
       <c r="M43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N43" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O43" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="P43" t="s">
         <v>30</v>
@@ -3811,25 +3796,25 @@
         <v>30</v>
       </c>
       <c r="R43" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="S43" t="s">
+        <v>82</v>
+      </c>
+      <c r="T43" t="s">
+        <v>81</v>
+      </c>
+      <c r="U43" t="s">
+        <v>30</v>
+      </c>
+      <c r="V43" t="s">
+        <v>30</v>
+      </c>
+      <c r="W43" t="s">
+        <v>85</v>
+      </c>
+      <c r="X43" t="s">
         <v>87</v>
-      </c>
-      <c r="T43" t="s">
-        <v>86</v>
-      </c>
-      <c r="U43" t="s">
-        <v>30</v>
-      </c>
-      <c r="V43" t="s">
-        <v>30</v>
-      </c>
-      <c r="W43" t="s">
-        <v>90</v>
-      </c>
-      <c r="X43" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:24">
@@ -3840,7 +3825,7 @@
         <v>24</v>
       </c>
       <c r="C44">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -3849,10 +3834,10 @@
         <v>3</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G44" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H44" t="s">
         <v>33</v>
@@ -3864,46 +3849,46 @@
         <v>30</v>
       </c>
       <c r="K44" t="s">
+        <v>30</v>
+      </c>
+      <c r="L44" t="s">
+        <v>30</v>
+      </c>
+      <c r="M44" t="s">
+        <v>63</v>
+      </c>
+      <c r="N44" t="s">
         <v>60</v>
       </c>
-      <c r="L44" t="s">
-        <v>30</v>
-      </c>
-      <c r="M44" t="s">
-        <v>69</v>
-      </c>
-      <c r="N44" t="s">
-        <v>61</v>
-      </c>
       <c r="O44" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="P44" t="s">
         <v>30</v>
       </c>
       <c r="Q44" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="R44" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="S44" t="s">
+        <v>78</v>
+      </c>
+      <c r="T44" t="s">
+        <v>66</v>
+      </c>
+      <c r="U44" t="s">
+        <v>30</v>
+      </c>
+      <c r="V44" t="s">
+        <v>30</v>
+      </c>
+      <c r="W44" t="s">
         <v>82</v>
       </c>
-      <c r="T44" t="s">
-        <v>67</v>
-      </c>
-      <c r="U44" t="s">
-        <v>30</v>
-      </c>
-      <c r="V44" t="s">
-        <v>79</v>
-      </c>
-      <c r="W44" t="s">
-        <v>85</v>
-      </c>
       <c r="X44" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:24">
@@ -3914,7 +3899,7 @@
         <v>24</v>
       </c>
       <c r="C45">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -3923,49 +3908,49 @@
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G45" t="s">
         <v>35</v>
       </c>
       <c r="H45" t="s">
+        <v>49</v>
+      </c>
+      <c r="I45" t="s">
+        <v>30</v>
+      </c>
+      <c r="J45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K45" t="s">
+        <v>30</v>
+      </c>
+      <c r="L45" t="s">
+        <v>30</v>
+      </c>
+      <c r="M45" t="s">
+        <v>34</v>
+      </c>
+      <c r="N45" t="s">
+        <v>58</v>
+      </c>
+      <c r="O45" t="s">
+        <v>69</v>
+      </c>
+      <c r="P45" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>30</v>
+      </c>
+      <c r="R45" t="s">
         <v>53</v>
       </c>
-      <c r="I45" t="s">
-        <v>30</v>
-      </c>
-      <c r="J45" t="s">
-        <v>30</v>
-      </c>
-      <c r="K45" t="s">
-        <v>59</v>
-      </c>
-      <c r="L45" t="s">
-        <v>30</v>
-      </c>
-      <c r="M45" t="s">
-        <v>57</v>
-      </c>
-      <c r="N45" t="s">
-        <v>65</v>
-      </c>
-      <c r="O45" t="s">
-        <v>72</v>
-      </c>
-      <c r="P45" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>79</v>
-      </c>
-      <c r="R45" t="s">
-        <v>54</v>
-      </c>
       <c r="S45" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="T45" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U45" t="s">
         <v>30</v>
@@ -3974,10 +3959,10 @@
         <v>30</v>
       </c>
       <c r="W45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X45" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:24">
@@ -3988,7 +3973,7 @@
         <v>24</v>
       </c>
       <c r="C46">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -4000,10 +3985,10 @@
         <v>47</v>
       </c>
       <c r="G46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I46" t="s">
         <v>30</v>
@@ -4012,46 +3997,46 @@
         <v>30</v>
       </c>
       <c r="K46" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L46" t="s">
         <v>30</v>
       </c>
       <c r="M46" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="N46" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="O46" t="s">
+        <v>60</v>
+      </c>
+      <c r="P46" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>30</v>
+      </c>
+      <c r="R46" t="s">
+        <v>79</v>
+      </c>
+      <c r="S46" t="s">
+        <v>81</v>
+      </c>
+      <c r="T46" t="s">
+        <v>76</v>
+      </c>
+      <c r="U46" t="s">
+        <v>30</v>
+      </c>
+      <c r="V46" t="s">
         <v>73</v>
       </c>
-      <c r="P46" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>30</v>
-      </c>
-      <c r="R46" t="s">
-        <v>77</v>
-      </c>
-      <c r="S46" t="s">
-        <v>87</v>
-      </c>
-      <c r="T46" t="s">
-        <v>84</v>
-      </c>
-      <c r="U46" t="s">
-        <v>30</v>
-      </c>
-      <c r="V46" t="s">
-        <v>79</v>
-      </c>
       <c r="W46" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="X46" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:24">
@@ -4062,7 +4047,7 @@
         <v>24</v>
       </c>
       <c r="C47">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -4071,13 +4056,13 @@
         <v>6</v>
       </c>
       <c r="F47" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G47" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I47" t="s">
         <v>30</v>
@@ -4086,46 +4071,46 @@
         <v>30</v>
       </c>
       <c r="K47" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L47" t="s">
         <v>30</v>
       </c>
       <c r="M47" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N47" t="s">
+        <v>60</v>
+      </c>
+      <c r="O47" t="s">
+        <v>69</v>
+      </c>
+      <c r="P47" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>30</v>
+      </c>
+      <c r="R47" t="s">
+        <v>53</v>
+      </c>
+      <c r="S47" t="s">
+        <v>75</v>
+      </c>
+      <c r="T47" t="s">
         <v>66</v>
       </c>
-      <c r="O47" t="s">
+      <c r="U47" t="s">
+        <v>30</v>
+      </c>
+      <c r="V47" t="s">
+        <v>73</v>
+      </c>
+      <c r="W47" t="s">
+        <v>63</v>
+      </c>
+      <c r="X47" t="s">
         <v>74</v>
-      </c>
-      <c r="P47" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>30</v>
-      </c>
-      <c r="R47" t="s">
-        <v>81</v>
-      </c>
-      <c r="S47" t="s">
-        <v>86</v>
-      </c>
-      <c r="T47" t="s">
-        <v>84</v>
-      </c>
-      <c r="U47" t="s">
-        <v>30</v>
-      </c>
-      <c r="V47" t="s">
-        <v>30</v>
-      </c>
-      <c r="W47" t="s">
-        <v>87</v>
-      </c>
-      <c r="X47" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:24">
@@ -4136,7 +4121,7 @@
         <v>24</v>
       </c>
       <c r="C48">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D48">
         <v>4</v>
@@ -4160,19 +4145,19 @@
         <v>30</v>
       </c>
       <c r="K48" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L48" t="s">
         <v>30</v>
       </c>
       <c r="M48" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N48" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O48" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="P48" t="s">
         <v>30</v>
@@ -4181,25 +4166,25 @@
         <v>30</v>
       </c>
       <c r="R48" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="S48" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T48" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="U48" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="V48" t="s">
         <v>30</v>
       </c>
       <c r="W48" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="X48" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:24">
@@ -4210,7 +4195,7 @@
         <v>24</v>
       </c>
       <c r="C49">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D49">
         <v>4</v>
@@ -4219,13 +4204,13 @@
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G49" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H49" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I49" t="s">
         <v>30</v>
@@ -4234,19 +4219,19 @@
         <v>30</v>
       </c>
       <c r="K49" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L49" t="s">
         <v>30</v>
       </c>
       <c r="M49" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="O49" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="P49" t="s">
         <v>30</v>
@@ -4255,13 +4240,13 @@
         <v>30</v>
       </c>
       <c r="R49" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="S49" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="T49" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="U49" t="s">
         <v>30</v>
@@ -4270,10 +4255,10 @@
         <v>30</v>
       </c>
       <c r="W49" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="X49" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:24">
@@ -4284,7 +4269,7 @@
         <v>25</v>
       </c>
       <c r="C50">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D50">
         <v>4</v>
@@ -4293,13 +4278,13 @@
         <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G50" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H50" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="I50" t="s">
         <v>30</v>
@@ -4308,19 +4293,19 @@
         <v>30</v>
       </c>
       <c r="K50" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L50" t="s">
         <v>30</v>
       </c>
       <c r="M50" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="O50" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="P50" t="s">
         <v>30</v>
@@ -4329,13 +4314,13 @@
         <v>30</v>
       </c>
       <c r="R50" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="S50" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="T50" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="U50" t="s">
         <v>30</v>
@@ -4344,10 +4329,10 @@
         <v>30</v>
       </c>
       <c r="W50" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="X50" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:24">
@@ -4358,7 +4343,7 @@
         <v>25</v>
       </c>
       <c r="C51">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -4367,13 +4352,13 @@
         <v>27</v>
       </c>
       <c r="F51" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H51" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="I51" t="s">
         <v>30</v>
@@ -4382,19 +4367,19 @@
         <v>30</v>
       </c>
       <c r="K51" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L51" t="s">
         <v>30</v>
       </c>
       <c r="M51" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="O51" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="P51" t="s">
         <v>30</v>
@@ -4403,13 +4388,13 @@
         <v>30</v>
       </c>
       <c r="R51" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="S51" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="T51" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="U51" t="s">
         <v>30</v>
@@ -4418,10 +4403,10 @@
         <v>30</v>
       </c>
       <c r="W51" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="X51" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:24">
@@ -4432,7 +4417,7 @@
         <v>25</v>
       </c>
       <c r="C52">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D52">
         <v>4</v>
@@ -4441,13 +4426,13 @@
         <v>28</v>
       </c>
       <c r="F52" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G52" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H52" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="I52" t="s">
         <v>30</v>
@@ -4456,19 +4441,19 @@
         <v>30</v>
       </c>
       <c r="K52" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L52" t="s">
         <v>30</v>
       </c>
       <c r="M52" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="O52" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="P52" t="s">
         <v>30</v>
@@ -4477,13 +4462,13 @@
         <v>30</v>
       </c>
       <c r="R52" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="S52" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="T52" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="U52" t="s">
         <v>30</v>
@@ -4492,10 +4477,10 @@
         <v>30</v>
       </c>
       <c r="W52" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="X52" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:24">
@@ -4506,7 +4491,7 @@
         <v>25</v>
       </c>
       <c r="C53">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D53">
         <v>4</v>
@@ -4515,13 +4500,13 @@
         <v>29</v>
       </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I53" t="s">
         <v>30</v>
@@ -4530,19 +4515,19 @@
         <v>30</v>
       </c>
       <c r="K53" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L53" t="s">
         <v>30</v>
       </c>
       <c r="M53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="O53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="P53" t="s">
         <v>30</v>
@@ -4551,13 +4536,13 @@
         <v>30</v>
       </c>
       <c r="R53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="S53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="T53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="U53" t="s">
         <v>30</v>
@@ -4566,10 +4551,10 @@
         <v>30</v>
       </c>
       <c r="W53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="X53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:24">
@@ -4580,7 +4565,7 @@
         <v>23</v>
       </c>
       <c r="C54">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D54">
         <v>5</v>
@@ -4589,13 +4574,13 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H54" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I54" t="s">
         <v>30</v>
@@ -4604,19 +4589,19 @@
         <v>30</v>
       </c>
       <c r="K54" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L54" t="s">
         <v>30</v>
       </c>
       <c r="M54" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="O54" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P54" t="s">
         <v>30</v>
@@ -4625,13 +4610,13 @@
         <v>30</v>
       </c>
       <c r="R54" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="S54" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="T54" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="U54" t="s">
         <v>30</v>
@@ -4640,10 +4625,10 @@
         <v>30</v>
       </c>
       <c r="W54" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="X54" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:24">
@@ -4654,7 +4639,7 @@
         <v>24</v>
       </c>
       <c r="C55">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D55">
         <v>5</v>
@@ -4663,13 +4648,13 @@
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G55" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H55" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I55" t="s">
         <v>30</v>
@@ -4678,19 +4663,19 @@
         <v>30</v>
       </c>
       <c r="K55" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="L55" t="s">
         <v>30</v>
       </c>
       <c r="M55" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="N55" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="O55" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="P55" t="s">
         <v>30</v>
@@ -4699,25 +4684,25 @@
         <v>30</v>
       </c>
       <c r="R55" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="S55" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="T55" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="U55" t="s">
         <v>30</v>
       </c>
       <c r="V55" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="W55" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="X55" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:24">
@@ -4728,7 +4713,7 @@
         <v>24</v>
       </c>
       <c r="C56">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D56">
         <v>5</v>
@@ -4737,13 +4722,13 @@
         <v>2</v>
       </c>
       <c r="F56" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G56" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H56" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="I56" t="s">
         <v>30</v>
@@ -4752,19 +4737,19 @@
         <v>30</v>
       </c>
       <c r="K56" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L56" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="M56" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="N56" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="O56" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="P56" t="s">
         <v>30</v>
@@ -4773,13 +4758,13 @@
         <v>30</v>
       </c>
       <c r="R56" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="S56" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="T56" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="U56" t="s">
         <v>30</v>
@@ -4788,10 +4773,10 @@
         <v>30</v>
       </c>
       <c r="W56" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="X56" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:24">
@@ -4802,7 +4787,7 @@
         <v>24</v>
       </c>
       <c r="C57">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D57">
         <v>5</v>
@@ -4811,13 +4796,13 @@
         <v>3</v>
       </c>
       <c r="F57" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G57" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H57" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="I57" t="s">
         <v>30</v>
@@ -4826,34 +4811,34 @@
         <v>30</v>
       </c>
       <c r="K57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L57" t="s">
         <v>30</v>
       </c>
       <c r="M57" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="N57" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="O57" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="P57" t="s">
         <v>30</v>
       </c>
       <c r="Q57" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="R57" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="S57" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="T57" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="U57" t="s">
         <v>30</v>
@@ -4862,10 +4847,10 @@
         <v>30</v>
       </c>
       <c r="W57" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="X57" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:24">
@@ -4876,7 +4861,7 @@
         <v>24</v>
       </c>
       <c r="C58">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D58">
         <v>5</v>
@@ -4885,13 +4870,13 @@
         <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G58" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="H58" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="I58" t="s">
         <v>30</v>
@@ -4900,19 +4885,19 @@
         <v>30</v>
       </c>
       <c r="K58" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="L58" t="s">
         <v>30</v>
       </c>
       <c r="M58" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="N58" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="O58" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="P58" t="s">
         <v>30</v>
@@ -4921,25 +4906,25 @@
         <v>30</v>
       </c>
       <c r="R58" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="S58" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="T58" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="U58" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="V58" t="s">
         <v>30</v>
       </c>
       <c r="W58" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="X58" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:24">
@@ -4950,7 +4935,7 @@
         <v>24</v>
       </c>
       <c r="C59">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D59">
         <v>5</v>
@@ -4959,13 +4944,13 @@
         <v>5</v>
       </c>
       <c r="F59" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G59" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H59" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="I59" t="s">
         <v>30</v>
@@ -4974,19 +4959,19 @@
         <v>30</v>
       </c>
       <c r="K59" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="L59" t="s">
         <v>30</v>
       </c>
       <c r="M59" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="N59" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="O59" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="P59" t="s">
         <v>30</v>
@@ -4995,13 +4980,13 @@
         <v>30</v>
       </c>
       <c r="R59" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="S59" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="T59" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="U59" t="s">
         <v>30</v>
@@ -5010,10 +4995,10 @@
         <v>30</v>
       </c>
       <c r="W59" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="X59" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:24">
@@ -5024,7 +5009,7 @@
         <v>24</v>
       </c>
       <c r="C60">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D60">
         <v>5</v>
@@ -5033,13 +5018,13 @@
         <v>6</v>
       </c>
       <c r="F60" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G60" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H60" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="I60" t="s">
         <v>30</v>
@@ -5048,19 +5033,19 @@
         <v>30</v>
       </c>
       <c r="K60" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="L60" t="s">
         <v>30</v>
       </c>
       <c r="M60" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="N60" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="O60" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="P60" t="s">
         <v>30</v>
@@ -5069,13 +5054,13 @@
         <v>30</v>
       </c>
       <c r="R60" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="S60" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="T60" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="U60" t="s">
         <v>30</v>
@@ -5084,10 +5069,10 @@
         <v>30</v>
       </c>
       <c r="W60" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="X60" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:24">
@@ -5098,7 +5083,7 @@
         <v>24</v>
       </c>
       <c r="C61">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D61">
         <v>5</v>
@@ -5107,13 +5092,13 @@
         <v>7</v>
       </c>
       <c r="F61" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G61" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H61" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I61" t="s">
         <v>30</v>
@@ -5122,19 +5107,19 @@
         <v>30</v>
       </c>
       <c r="K61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L61" t="s">
         <v>30</v>
       </c>
       <c r="M61" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="N61" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="O61" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="P61" t="s">
         <v>30</v>
@@ -5143,13 +5128,13 @@
         <v>30</v>
       </c>
       <c r="R61" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="S61" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="T61" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="U61" t="s">
         <v>30</v>
@@ -5158,10 +5143,10 @@
         <v>30</v>
       </c>
       <c r="W61" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="X61" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:24">
@@ -5172,7 +5157,7 @@
         <v>24</v>
       </c>
       <c r="C62">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D62">
         <v>5</v>
@@ -5181,13 +5166,13 @@
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="G62" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H62" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I62" t="s">
         <v>30</v>
@@ -5196,34 +5181,34 @@
         <v>30</v>
       </c>
       <c r="K62" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="L62" t="s">
         <v>30</v>
       </c>
       <c r="M62" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="N62" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="O62" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="P62" t="s">
         <v>30</v>
       </c>
       <c r="Q62" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="R62" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="S62" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="T62" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="U62" t="s">
         <v>30</v>
@@ -5232,10 +5217,10 @@
         <v>30</v>
       </c>
       <c r="W62" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="X62" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:24">
@@ -5246,7 +5231,7 @@
         <v>25</v>
       </c>
       <c r="C63">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D63">
         <v>5</v>
@@ -5255,13 +5240,13 @@
         <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G63" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H63" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I63" t="s">
         <v>30</v>
@@ -5270,34 +5255,34 @@
         <v>30</v>
       </c>
       <c r="K63" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L63" t="s">
         <v>30</v>
       </c>
       <c r="M63" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="N63" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="O63" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="P63" t="s">
         <v>30</v>
       </c>
       <c r="Q63" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="R63" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="S63" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="T63" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="U63" t="s">
         <v>30</v>
@@ -5306,10 +5291,10 @@
         <v>30</v>
       </c>
       <c r="W63" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="X63" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:24">
@@ -5320,7 +5305,7 @@
         <v>25</v>
       </c>
       <c r="C64">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D64">
         <v>5</v>
@@ -5329,13 +5314,13 @@
         <v>27</v>
       </c>
       <c r="F64" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H64" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="I64" t="s">
         <v>30</v>
@@ -5344,19 +5329,19 @@
         <v>30</v>
       </c>
       <c r="K64" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L64" t="s">
         <v>30</v>
       </c>
       <c r="M64" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="N64" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="O64" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="P64" t="s">
         <v>30</v>
@@ -5365,25 +5350,25 @@
         <v>30</v>
       </c>
       <c r="R64" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="S64" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="T64" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="U64" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="V64" t="s">
         <v>30</v>
       </c>
       <c r="W64" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="X64" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:24">
@@ -5394,7 +5379,7 @@
         <v>25</v>
       </c>
       <c r="C65">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D65">
         <v>5</v>
@@ -5403,13 +5388,13 @@
         <v>28</v>
       </c>
       <c r="F65" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G65" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H65" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="I65" t="s">
         <v>30</v>
@@ -5418,19 +5403,19 @@
         <v>30</v>
       </c>
       <c r="K65" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L65" t="s">
         <v>30</v>
       </c>
       <c r="M65" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="N65" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="O65" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="P65" t="s">
         <v>30</v>
@@ -5439,25 +5424,25 @@
         <v>30</v>
       </c>
       <c r="R65" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="S65" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="T65" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="U65" t="s">
         <v>30</v>
       </c>
       <c r="V65" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="W65" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="X65" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:24">
@@ -5468,7 +5453,7 @@
         <v>25</v>
       </c>
       <c r="C66">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D66">
         <v>5</v>
@@ -5477,13 +5462,13 @@
         <v>29</v>
       </c>
       <c r="F66" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H66" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I66" t="s">
         <v>30</v>
@@ -5492,19 +5477,19 @@
         <v>30</v>
       </c>
       <c r="K66" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L66" t="s">
         <v>30</v>
       </c>
       <c r="M66" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="N66" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="O66" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="P66" t="s">
         <v>30</v>
@@ -5513,13 +5498,13 @@
         <v>30</v>
       </c>
       <c r="R66" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="S66" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="T66" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="U66" t="s">
         <v>30</v>
@@ -5528,10 +5513,10 @@
         <v>30</v>
       </c>
       <c r="W66" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="X66" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
